--- a/out/LSTM-Mamba1_repeat_2_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6899601950856026</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6899601950856026</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.0899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.0899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>5.326153625547767</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.0899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.265252384310588e-05</v>
+        <v>-6.522884500527289e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03989348670157599</v>
+        <v>0.02808564681070064</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.0798934385716645</v>
+        <v>0.05624624678713619</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1541288095514164</v>
+        <v>0.1085088794383322</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3483612452033022</v>
+        <v>0.2452518374137715</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04741139483149086</v>
+        <v>0.03337793958473097</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2888584543988409</v>
+        <v>0.2033608363725715</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.009620124688019947</v>
+        <v>0.006772323509422399</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2606131383407945</v>
+        <v>0.1834748228730182</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.008330698571314828</v>
+        <v>0.005863566622783443</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2676445325727835</v>
+        <v>0.1884236426376505</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004069803192927953</v>
+        <v>0.002863672648104922</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2674455436646542</v>
+        <v>0.1882820691942722</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00194004755993306</v>
+        <v>0.001364083631158653</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2672508364748079</v>
+        <v>0.188143505866406</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0008050133454241756</v>
+        <v>0.0005656279581166873</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2669191398657209</v>
+        <v>0.187908437385919</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005567768447390168</v>
+        <v>0.0003900958028933744</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2672263895694539</v>
+        <v>0.1881232567927102</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002295204766138316</v>
+        <v>0.0001599374780580794</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2671280429886996</v>
+        <v>0.1880524789126902</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001166072332215104</v>
+        <v>8.052596622172162e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2671314925649534</v>
+        <v>0.1880534453850971</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.276263186697116e-05</v>
+        <v>2.859130153281488e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2671002674980336</v>
+        <v>0.1880298579022884</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.0768496760115e-05</v>
+        <v>1.332426436274844e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.267099561866316</v>
+        <v>0.1880279254918529</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.987449840330433e-06</v>
+        <v>4.034747715012475e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2670941658485564</v>
+        <v>0.1880226420301429</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2670884188930199</v>
+        <v>0.1880170900940134</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.232968880383854e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2670825511050653</v>
+        <v>0.1880114398288601</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2670772608629637</v>
+        <v>0.1880061985075593</v>
       </c>
     </row>
     <row r="61">
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2670719729241133</v>
+        <v>0.1880009105687088</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2670667010900623</v>
+        <v>0.1879956387346578</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2670667808010068</v>
+        <v>0.1879957184456023</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2670667728299124</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2670669322518015</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2670671873268243</v>
+        <v>0.1879961249714198</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.267066940222896</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2670669003674236</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.267066940222896</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2670670358760296</v>
+        <v>0.1879959735206251</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2670669721072738</v>
+        <v>0.1879959097518693</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2670669322518015</v>
+        <v>0.187995869896397</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.26706666123459</v>
+        <v>0.1879955988791855</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2670665815236452</v>
+        <v>0.1879955191682407</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2670666293502119</v>
+        <v>0.1879955669948075</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.267066748916629</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2670667329744401</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.267066748916629</v>
+        <v>0.1879956865612245</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2670667329744401</v>
+        <v>0.1879956706190356</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.267066940222896</v>
+        <v>0.1879958778674914</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2670671554424465</v>
+        <v>0.187996093087042</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2670670677604075</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2670670199338407</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2670670677604075</v>
+        <v>0.187996005405003</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2670668844252347</v>
+        <v>0.1879958220698303</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2670668923963292</v>
+        <v>0.1879958300409247</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2670669003674236</v>
+        <v>0.1879958380120192</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.1879958459831136</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2670669481939904</v>
+        <v>0.1879958858385859</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2670670119627463</v>
+        <v>0.1879959496073418</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2670671235580687</v>
+        <v>0.1879960612026642</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2670671713846354</v>
+        <v>0.1879961090292309</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2670671315291631</v>
+        <v>0.1879960691737586</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.267067059789313</v>
+        <v>0.1879959974339085</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2670671793557298</v>
+        <v>0.1879961170003253</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2670670199338407</v>
+        <v>0.1879959575784362</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.1879957264166968</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2670667728299124</v>
+        <v>0.1879957104745079</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2670667568877235</v>
+        <v>0.187995694532319</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2670666373213064</v>
+        <v>0.1879955749659019</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2670665974658341</v>
+        <v>0.1879955351104296</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2670668764541403</v>
+        <v>0.1879958140987358</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2670668605119514</v>
+        <v>0.1879957981565469</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2670667967431957</v>
+        <v>0.1879957343877912</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2670666931189678</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2670665735525508</v>
+        <v>0.1879955111971462</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2670666931189678</v>
+        <v>0.1879956307635633</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.1879956785901301</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.267066836598668</v>
+        <v>0.1879957742432635</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2670667170322512</v>
+        <v>0.1879956546768467</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2670667250033457</v>
+        <v>0.1879956626479412</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.6899601950856026</v>
+        <v>0.9417324822465817</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>5.326153625547767</v>
+        <v>1.990866241123291</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>5.326153625547767</v>
+        <v>3.04</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>5.326153625547767</v>
+        <v>1.990866241123291</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.0899601950856026</v>
+        <v>0.9417324822465817</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.0899601950856026</v>
+        <v>-0.1074012766301274</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6899601950856026</v>
+        <v>0.9417324822465817</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>5.326153625547767</v>
+        <v>1.990866241123291</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>5.326153625547767</v>
+        <v>3.04</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>5.326153625547767</v>
+        <v>3.04</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>5.326153625547767</v>
+        <v>3.04</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>5.326153625547767</v>
+        <v>3.04</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>5.326153625547767</v>
+        <v>1.990866241123291</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.0899601950856026</v>
+        <v>0.9417324822465817</v>
       </c>
       <c r="JC43" t="n">
-        <v>-9.265252384310588e-05</v>
+        <v>-0.0001769162508650916</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.03989348670157599</v>
+        <v>0.07617489397627043</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.0798934385716645</v>
+        <v>0.1525532935754464</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1541288095514164</v>
+        <v>0.2943047281487349</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3483612452033022</v>
+        <v>0.6651824410002246</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.04741139483149086</v>
+        <v>0.09052978416602225</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2888584543988409</v>
+        <v>0.5515647162328039</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.009620124688019947</v>
+        <v>0.01836896006198707</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2606131383407945</v>
+        <v>0.4976316407959857</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.008330698571314828</v>
+        <v>0.01590869357147882</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2676445325727835</v>
+        <v>0.5110593471586791</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.004069803192927953</v>
+        <v>0.007776397061086948</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.2674455436646542</v>
+        <v>0.5106839291051845</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00194004755993306</v>
+        <v>0.003708697814533818</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.2672508364748079</v>
+        <v>0.5103167193624277</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0008050133454241756</v>
+        <v>0.001542097654250023</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.2669191398657209</v>
+        <v>0.5096879532089904</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0005567768447390168</v>
+        <v>0.001066851699646283</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.2672263895694539</v>
+        <v>0.5102789305693172</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0002295204766138316</v>
+        <v>0.0004427794814467389</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.2671280429886996</v>
+        <v>0.5100957001472723</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0001166072332215104</v>
+        <v>0.0002268555490541985</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.2671314925649534</v>
+        <v>0.5101068339669295</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>4.276263186697116e-05</v>
+        <v>8.632635104234045e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.2671002674980336</v>
+        <v>0.5100516893334787</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>2.0768496760115e-05</v>
+        <v>4.481909373622233e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.267099561866316</v>
+        <v>0.5100548993141285</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>7.987449840330433e-06</v>
+        <v>1.928088448409603e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.2670941658485564</v>
+        <v>0.5100491509620053</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>8.610817715762575e-07</v>
+        <v>6.722163543152517e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.2670884188930199</v>
+        <v>0.5100427208196879</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-2.232968880383854e-06</v>
+        <v>7.289038596293463e-08</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.2670825511050653</v>
+        <v>0.5100361298751046</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-3.759791964848896e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2670772608629637</v>
+        <v>0.5100305983117023</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.68213567138761e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2670719729241133</v>
+        <v>0.5100250214545515</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2670667010900623</v>
+        <v>0.5100196141118946</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.5100146929581731</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2670667808010068</v>
+        <v>0.5100147328136454</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2670667728299124</v>
+        <v>0.5100147248425509</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2670669322518015</v>
+        <v>0.5100148842644401</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2670671873268243</v>
+        <v>0.5100151393394629</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.267066940222896</v>
+        <v>0.5100148922355345</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2670669003674236</v>
+        <v>0.5100148523800622</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.5100148603511567</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.267066940222896</v>
+        <v>0.5100148922355345</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2670670358760296</v>
+        <v>0.5100149878886682</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2670669721072738</v>
+        <v>0.5100149241199123</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2670669322518015</v>
+        <v>0.5100148842644401</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.5100148603511567</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.26706666123459</v>
+        <v>0.5100146132472285</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2670665815236452</v>
+        <v>0.5100145335362838</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2670666293502119</v>
+        <v>0.5100145813628505</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.267066748916629</v>
+        <v>0.5100147009292676</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2670667329744401</v>
+        <v>0.5100146849870787</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.267066748916629</v>
+        <v>0.5100147009292676</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2670667329744401</v>
+        <v>0.5100146849870787</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.5100147407847399</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.5100147407847399</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.5100147407847399</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.267066940222896</v>
+        <v>0.5100148922355345</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2670671554424465</v>
+        <v>0.510015107455085</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2670670677604075</v>
+        <v>0.510015019773046</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2670670199338407</v>
+        <v>0.5100149719464793</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2670670677604075</v>
+        <v>0.510015019773046</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2670668844252347</v>
+        <v>0.5100148364378733</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2670668923963292</v>
+        <v>0.5100148444089677</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2670669003674236</v>
+        <v>0.5100148523800622</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.5100148603511567</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2670669083385181</v>
+        <v>0.5100148603511567</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2670669481939904</v>
+        <v>0.510014900206629</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2670670119627463</v>
+        <v>0.5100149639753848</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2670671235580687</v>
+        <v>0.5100150755707072</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2670671713846354</v>
+        <v>0.510015123397274</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2670671315291631</v>
+        <v>0.5100150835418017</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.267067059789313</v>
+        <v>0.5100150118019515</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2670671793557298</v>
+        <v>0.5100151313683684</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2670670199338407</v>
+        <v>0.5100149719464793</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2670667887721013</v>
+        <v>0.5100147407847399</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.5100146929581731</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2670667728299124</v>
+        <v>0.5100147248425509</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2670667568877235</v>
+        <v>0.510014708900362</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2670666373213064</v>
+        <v>0.5100145893339449</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2670665974658341</v>
+        <v>0.5100145494784727</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.5100146929581731</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2670668764541403</v>
+        <v>0.5100148284667788</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2670668605119514</v>
+        <v>0.5100148125245899</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2670667967431957</v>
+        <v>0.5100147487558343</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2670666931189678</v>
+        <v>0.5100146451316063</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2670665735525508</v>
+        <v>0.5100145255651893</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2670666931189678</v>
+        <v>0.5100146451316063</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2670667409455346</v>
+        <v>0.5100146929581731</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.267066836598668</v>
+        <v>0.5100147886113066</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2670667170322512</v>
+        <v>0.5100146690448898</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6899601950856026</v>
+        <v>-0.3074012766301275</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2670667250033457</v>
+        <v>0.5100146770159842</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01067247521132231</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.006046375259757042</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9299999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003545502200722694</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002212170511484146</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001423189416527748</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0008787233382463455</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0006479490548372269</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0004879944026470184</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0003102105110883713</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.000272553414106369</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.0002100206911563873</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0001778211444616318</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-6.490759551525116e-05</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9417324822465817</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>5.591660737991333e-05</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.990866241123291</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0001019183546304703</v>
       </c>
       <c r="JB16" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>9.916722774505615e-06</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.990866241123291</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0002324692904949188</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.9417324822465817</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0004175789654254913</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.1074012766301274</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0005439240485429764</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.0006999466568231583</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0008046943694353104</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0008144751191139221</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0007585659623146057</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0006434135138988495</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.000612989068031311</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0005794502794742584</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0005327891558408737</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0004903022199869156</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0003906358033418655</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0002291444689035416</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.0002251621335744858</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0001856721937656403</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0001411028206348419</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-7.948465645313263e-05</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-1.043081283569336e-07</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9417324822465817</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.0001132376492023468</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.990866241123291</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0002094656229019165</v>
       </c>
       <c r="JB38" t="n">
-        <v>3.04</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.000262940302491188</v>
       </c>
       <c r="JB39" t="n">
-        <v>3.04</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.0003610681742429733</v>
       </c>
       <c r="JB40" t="n">
-        <v>3.04</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.000302482396364212</v>
       </c>
       <c r="JB41" t="n">
-        <v>3.04</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0002766959369182587</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.990866241123291</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-3.860518336296082e-05</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.9417324822465817</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001769162508650916</v>
+        <v>-7.549743061384651e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.07617489397627043</v>
+        <v>0.03250700163653785</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0003626290708780289</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1525532935754464</v>
+        <v>0.06510075586587261</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2943047281487349</v>
+        <v>0.1255909113784595</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001137476414442062</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6651824410002246</v>
+        <v>0.2838603620831945</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.09052978416602225</v>
+        <v>0.03863297737825833</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.002493893727660179</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5515647162328039</v>
+        <v>0.2353747611161221</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01836896006198707</v>
+        <v>0.00783871192263551</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.003375468775629997</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4976316407959857</v>
+        <v>0.2123591837899089</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01590869357147882</v>
+        <v>0.006787130236714228</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.004143976606428623</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.5110593471586791</v>
+        <v>0.2180879121040965</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007776397061086948</v>
+        <v>0.003315884100197597</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004364960826933384</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.5106839291051845</v>
+        <v>0.217924827968996</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003708697814533818</v>
+        <v>0.001579903061546279</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00443989597260952</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.5103167193624277</v>
+        <v>0.2177652469128931</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001542097654250023</v>
+        <v>0.0006552583008062353</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.004348873160779476</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.5096879532089904</v>
+        <v>0.2174940408466905</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001066851699646283</v>
+        <v>0.0004526011935854903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.004295076243579388</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.5102789305693172</v>
+        <v>0.217743387102616</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0004427794814467389</v>
+        <v>0.0001857089590046543</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.004044136963784695</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.5100957001472723</v>
+        <v>0.2176623513565788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002268555490541985</v>
+        <v>9.388939844386562e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003903652541339397</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.5101068339669295</v>
+        <v>0.2176642463538488</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>8.632635104234045e-05</v>
+        <v>3.383994239731721e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003964175470173359</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5100516893334787</v>
+        <v>0.2176377769955543</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.481909373622233e-05</v>
+        <v>1.618743066942789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.003957471810281277</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.5100548993141285</v>
+        <v>0.2176363164230874</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.928088448409603e-05</v>
+        <v>5.728762911577315e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003965175710618496</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.5100491509620053</v>
+        <v>0.2176309892779815</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.722163543152517e-06</v>
+        <v>-2.045694596194254e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003830960020422935</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.5100427208196879</v>
+        <v>0.2176253723353827</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>7.289038596293463e-08</v>
+        <v>-2.694140733653212e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.003639472648501396</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.5100361298751046</v>
+        <v>0.2176196491787541</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.932986608081494e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003451590426266193</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5100305983117023</v>
+        <v>0.2176144078574532</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003261948935687542</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.5100250214545515</v>
+        <v>0.2176091199186027</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.003089628182351589</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.5100196141118946</v>
+        <v>0.2176038480845517</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002907158806920052</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5100146929581731</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002859583124518394</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5100147328136454</v>
+        <v>0.2176039277954963</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002736752852797508</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5100147248425509</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002775590866804123</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5100148842644401</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002671336755156517</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.00284898467361927</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5100151393394629</v>
+        <v>0.2176043343213138</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003075116313993931</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5100148922355345</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.003157760016620159</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5100148523800622</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003228937275707722</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003232407383620739</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5100148603511567</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003172636032104492</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002735365182161331</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5100148922355345</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002846803516149521</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5100149878886682</v>
+        <v>0.2176041828705191</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003199335187673569</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5100149241199123</v>
+        <v>0.2176041191017632</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.003433937206864357</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5100148842644401</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.003402662463486195</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5100148603511567</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.003296910785138607</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5100146132472285</v>
+        <v>0.2176038082290795</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003131265752017498</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5100145335362838</v>
+        <v>0.2176037285181347</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.00291701965034008</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5100145813628505</v>
+        <v>0.2176037763447014</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002792024984955788</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5100147009292676</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002648239955306053</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5100146849870787</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002569770440459251</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5100147009292676</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.002503026276826859</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5100146849870787</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002513408660888672</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5100147407847399</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002583066001534462</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5100147407847399</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.00245639868080616</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5100147407847399</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.002569438889622688</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5100148922355345</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.002573518082499504</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.16</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.510015107455085</v>
+        <v>0.217604302436936</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.002841517329216003</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.510015019773046</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.003006413578987122</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5100149719464793</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.003098845481872559</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.510015019773046</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.003148803487420082</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5100148364378733</v>
+        <v>0.2176040314197242</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.003125406801700592</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5100148444089677</v>
+        <v>0.2176040393908187</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00300881639122963</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5100148523800622</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.002975475043058395</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5100148603511567</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.002925489097833633</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5100148603511567</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.002758214250206947</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.510014900206629</v>
+        <v>0.2176040951884799</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002752466127276421</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5100149639753848</v>
+        <v>0.2176041589572358</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.002835297957062721</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5100150755707072</v>
+        <v>0.2176042705525581</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.003036163747310638</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.510015123397274</v>
+        <v>0.2176043183791249</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003135218285024166</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5100150835418017</v>
+        <v>0.2176042785236526</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003154230304062366</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5100150118019515</v>
+        <v>0.2176042067838025</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003221052698791027</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5100151313683684</v>
+        <v>0.2176043263502193</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.003226570785045624</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5100149719464793</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.00324644148349762</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5100147407847399</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.003169804811477661</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5100146929581731</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.00308682955801487</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5100147248425509</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.002955095842480659</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.002902241423726082</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.3</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002827813848853111</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.510014708900362</v>
+        <v>0.2176039038822129</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.002705935388803482</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5100145893339449</v>
+        <v>0.2176037843157959</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.00255792960524559</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5100145494784727</v>
+        <v>0.2176037444603236</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.002446757629513741</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5100146929581731</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.002451041713356972</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5100148284667788</v>
+        <v>0.2176040234486298</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.00254148431122303</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5100148125245899</v>
+        <v>0.2176040075064408</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.002576394006609917</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.002582153305411339</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5100147487558343</v>
+        <v>0.2176039437376852</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.002523822709918022</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5100146451316063</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.002384975552558899</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5100145255651893</v>
+        <v>0.2176037205470402</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002424390986561775</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5100146451316063</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.00243554450571537</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5100146929581731</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002536626532673836</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.3074012766301275</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5100147886113066</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002564083784818649</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.09000000000000052</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5100146690448898</v>
+        <v>0.2176038640267406</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002501415088772774</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.3074012766301275</v>
+        <v>-0.3000000000000006</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5100146770159842</v>
+        <v>0.2176038719978351</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000001.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01067247521132231</v>
+        <v>-0.01067246682941914</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.006046375259757042</v>
+        <v>-0.00604636874049902</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9299999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.003545502200722694</v>
+        <v>-0.003545487299561501</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.5799999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.002212170511484146</v>
+        <v>-0.0022121611982584</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.3</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001423189416527748</v>
+        <v>-0.001423170790076256</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.02000000000000007</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0008787233382463455</v>
+        <v>-0.0008787084370851517</v>
       </c>
       <c r="JB7" t="n">
         <v>0.8599999999999999</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0006479490548372269</v>
+        <v>-0.0006479248404502869</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0004879944026470184</v>
+        <v>-0.0004879795014858246</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0003102105110883713</v>
+        <v>-0.000310191884636879</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.000272553414106369</v>
+        <v>-0.0002725441008806229</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.0002100206911563873</v>
+        <v>-0.0002100151032209396</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0001778211444616318</v>
+        <v>-0.0001778118312358856</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-6.490759551525116e-05</v>
+        <v>-6.491690874099731e-05</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>5.591660737991333e-05</v>
+        <v>5.592033267021179e-05</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0001019183546304703</v>
+        <v>0.000101923942565918</v>
       </c>
       <c r="JB16" t="n">
         <v>0.2599999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>9.916722774505615e-06</v>
+        <v>9.931623935699463e-06</v>
       </c>
       <c r="JB17" t="n">
         <v>0.1199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.0002324692904949188</v>
+        <v>-0.0002324599772691727</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.02000000000000007</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.0004175789654254913</v>
+        <v>-0.0004175677895545959</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.16</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.0005439240485429764</v>
+        <v>-0.0005439184606075287</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.0006999466568231583</v>
+        <v>-0.0006999373435974121</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0008046943694353104</v>
+        <v>-0.0008046850562095642</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0007585659623146057</v>
+        <v>-0.0007585640996694565</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0006434135138988495</v>
+        <v>-0.0006433986127376556</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.02000000000000007</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.000612989068031311</v>
+        <v>-0.0006129778921604156</v>
       </c>
       <c r="JB26" t="n">
         <v>0.7199999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0005794502794742584</v>
+        <v>-0.0005794558674097061</v>
       </c>
       <c r="JB27" t="n">
         <v>0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0005327891558408737</v>
+        <v>-0.0005327798426151276</v>
       </c>
       <c r="JB28" t="n">
         <v>0.9999999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0004903022199869156</v>
+        <v>-0.0004902947694063187</v>
       </c>
       <c r="JB29" t="n">
         <v>0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.0003906358033418655</v>
+        <v>-0.0003906227648258209</v>
       </c>
       <c r="JB30" t="n">
         <v>0.9999999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0002291444689035416</v>
+        <v>-0.0002291183918714523</v>
       </c>
       <c r="JB31" t="n">
         <v>0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.0002251621335744858</v>
+        <v>-0.0002251528203487396</v>
       </c>
       <c r="JB32" t="n">
         <v>0.9999999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0001856721937656403</v>
+        <v>-0.000185670331120491</v>
       </c>
       <c r="JB33" t="n">
         <v>0.9999999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0001411028206348419</v>
+        <v>-0.0001411009579896927</v>
       </c>
       <c r="JB34" t="n">
         <v>0.9999999999999998</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-7.948465645313263e-05</v>
+        <v>-7.947906851768494e-05</v>
       </c>
       <c r="JB35" t="n">
         <v>0.9999999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-1.043081283569336e-07</v>
+        <v>-1.080334186553955e-07</v>
       </c>
       <c r="JB36" t="n">
         <v>0.9999999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.0001132376492023468</v>
+        <v>0.0001132544130086899</v>
       </c>
       <c r="JB37" t="n">
         <v>0.3999999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.0002094656229019165</v>
+        <v>0.0002094842493534088</v>
       </c>
       <c r="JB38" t="n">
         <v>0.3999999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.000262940302491188</v>
+        <v>0.0002629272639751434</v>
       </c>
       <c r="JB39" t="n">
         <v>0.3999999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.0003610681742429733</v>
+        <v>0.0003610774874687195</v>
       </c>
       <c r="JB40" t="n">
         <v>0.3999999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.000302482396364212</v>
+        <v>0.0003024935722351074</v>
       </c>
       <c r="JB41" t="n">
         <v>0.2599999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.0002766959369182587</v>
+        <v>0.0002766940742731094</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.02000000000000007</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-3.860518336296082e-05</v>
+        <v>-3.859773278236389e-05</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.3</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0003626290708780289</v>
+        <v>-0.0003626327961683273</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.5799999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.001137476414442062</v>
+        <v>-0.001137493178248405</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.002493893727660179</v>
+        <v>-0.002493897452950478</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.003375468775629997</v>
+        <v>-0.003375464119017124</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.004143976606428623</v>
+        <v>-0.004143974743783474</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.004364960826933384</v>
+        <v>-0.004364973865449429</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.00443989597260952</v>
+        <v>-0.004439922049641609</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.004348873160779476</v>
+        <v>-0.004348880611360073</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.004295076243579388</v>
+        <v>-0.004295080900192261</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.004044136963784695</v>
+        <v>-0.004044145345687866</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.003903652541339397</v>
+        <v>-0.003903664648532867</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.003964175470173359</v>
+        <v>-0.003964160569012165</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.003957471810281277</v>
+        <v>-0.003957461565732956</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.003965175710618496</v>
+        <v>-0.003965155221521854</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.003830960020422935</v>
+        <v>-0.003830953501164913</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.003451590426266193</v>
+        <v>-0.003451600670814514</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.003261948935687542</v>
+        <v>-0.003261968493461609</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.003089628182351589</v>
+        <v>-0.003089639358222485</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.002907158806920052</v>
+        <v>-0.002907166257500648</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002859583124518394</v>
+        <v>-0.002859599888324738</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002775590866804123</v>
+        <v>-0.002775585278868675</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.2599999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002671336755156517</v>
+        <v>-0.002671338617801666</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.2599999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.00284898467361927</v>
+        <v>-0.002848988398909569</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.2599999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003075116313993931</v>
+        <v>-0.003075104206800461</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.2599999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.003228937275707722</v>
+        <v>-0.003228927962481976</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.1199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.003232407383620739</v>
+        <v>-0.003232409246265888</v>
       </c>
       <c r="JB72" t="n">
         <v>0.16</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.003172636032104492</v>
+        <v>-0.003172628581523895</v>
       </c>
       <c r="JB73" t="n">
         <v>0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.002735365182161331</v>
+        <v>-0.002735385671257973</v>
       </c>
       <c r="JB74" t="n">
         <v>0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.002846803516149521</v>
+        <v>-0.002846814692020416</v>
       </c>
       <c r="JB75" t="n">
         <v>0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003199335187673569</v>
+        <v>-0.003199351951479912</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.003433937206864357</v>
+        <v>-0.003433947451412678</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.003402662463486195</v>
+        <v>-0.003402660600841045</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.003296910785138607</v>
+        <v>-0.003296934068202972</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.003131265752017498</v>
+        <v>-0.003131281584501266</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.00291701965034008</v>
+        <v>-0.002917010337114334</v>
       </c>
       <c r="JB81" t="n">
         <v>0.7199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002792024984955788</v>
+        <v>-0.002792023122310638</v>
       </c>
       <c r="JB82" t="n">
         <v>0.8599999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002648239955306053</v>
+        <v>-0.002648254856467247</v>
       </c>
       <c r="JB83" t="n">
         <v>0.9999999999999998</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.002569770440459251</v>
+        <v>-0.002569789066910744</v>
       </c>
       <c r="JB84" t="n">
         <v>0.9999999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.002503026276826859</v>
+        <v>-0.002503033727407455</v>
       </c>
       <c r="JB85" t="n">
         <v>0.9999999999999998</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002513408660888672</v>
+        <v>-0.00251341424882412</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.002583066001534462</v>
+        <v>-0.002583064138889313</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.00245639868080616</v>
+        <v>-0.002456406131386757</v>
       </c>
       <c r="JB88" t="n">
         <v>0.8599999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.002569438889622688</v>
+        <v>-0.002569450065493584</v>
       </c>
       <c r="JB89" t="n">
         <v>0.1199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.002573518082499504</v>
+        <v>-0.002573521807789803</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.16</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.002841517329216003</v>
+        <v>-0.002841547131538391</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.4399999999999999</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.003006413578987122</v>
+        <v>-0.003006432205438614</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.7199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.003098845481872559</v>
+        <v>-0.003098858520388603</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.8599999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.003148803487420082</v>
+        <v>-0.003148818388581276</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.003125406801700592</v>
+        <v>-0.00312542449682951</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.8599999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00300881639122963</v>
+        <v>-0.003008823841810226</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.7199999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.002975475043058395</v>
+        <v>-0.002975482493638992</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.002925489097833633</v>
+        <v>-0.002925494685769081</v>
       </c>
       <c r="JB98" t="n">
         <v>0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.002758214250206947</v>
+        <v>-0.002758216112852097</v>
       </c>
       <c r="JB99" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.002752466127276421</v>
+        <v>-0.002752460539340973</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.002835297957062721</v>
+        <v>-0.00283529981970787</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.003036163747310638</v>
+        <v>-0.003036182373762131</v>
       </c>
       <c r="JB102" t="n">
         <v>0.02000000000000007</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.003135218285024166</v>
+        <v>-0.003135238774120808</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.8599999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.003154230304062366</v>
+        <v>-0.003154243342578411</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.003221052698791027</v>
+        <v>-0.003221086226403713</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.003226570785045624</v>
+        <v>-0.003226589411497116</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.00324644148349762</v>
+        <v>-0.00324648804962635</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.003169804811477661</v>
+        <v>-0.003169834613800049</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.00308682955801487</v>
+        <v>-0.003086844459176064</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.002955095842480659</v>
+        <v>-0.002955099567770958</v>
       </c>
       <c r="JB110" t="n">
         <v>0.02000000000000007</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.002827813848853111</v>
+        <v>-0.002827832475304604</v>
       </c>
       <c r="JB112" t="n">
         <v>0.5799999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.002705935388803482</v>
+        <v>-0.002705937251448631</v>
       </c>
       <c r="JB113" t="n">
         <v>0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.00255792960524559</v>
+        <v>-0.002557931467890739</v>
       </c>
       <c r="JB114" t="n">
         <v>0.8599999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.002446757629513741</v>
+        <v>-0.002446768805384636</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.002451041713356972</v>
+        <v>-0.002451039850711823</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.00254148431122303</v>
+        <v>-0.002541506662964821</v>
       </c>
       <c r="JB117" t="n">
         <v>0.8599999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.002576394006609917</v>
+        <v>-0.002576412633061409</v>
       </c>
       <c r="JB118" t="n">
         <v>0.7199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.002582153305411339</v>
+        <v>-0.002582158893346786</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.002523822709918022</v>
+        <v>-0.002523835748434067</v>
       </c>
       <c r="JB120" t="n">
         <v>0.1199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.002384975552558899</v>
+        <v>-0.002384986728429794</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.002424390986561775</v>
+        <v>-0.002424418926239014</v>
       </c>
       <c r="JB122" t="n">
         <v>0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.00243554450571537</v>
+        <v>-0.002435572445392609</v>
       </c>
       <c r="JB123" t="n">
         <v>0.2599999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002536626532673836</v>
+        <v>-0.002536633983254433</v>
       </c>
       <c r="JB124" t="n">
         <v>0.1199999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002564083784818649</v>
+        <v>-0.002564089372754097</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.09000000000000052</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002501415088772774</v>
+        <v>-0.002501413226127625</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.3000000000000006</v>
